--- a/docs/files/rocscience/vp029.xlsx
+++ b/docs/files/rocscience/vp029.xlsx
@@ -17201,10 +17201,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>131.484</v>
+        <v>-6.589</v>
       </c>
       <c r="C3" s="3">
-        <v>148.399</v>
+        <v>410.231</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>-120.321</v>
+        <v>-139.352</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -17403,17 +17403,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>136.0</v>
-      </c>
-      <c r="B3" s="3">
-        <v>-119.6</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
       <c r="E3" t="s">
         <v>40</v>
       </c>
@@ -17422,17 +17414,9 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>137.767</v>
-      </c>
-      <c r="B4" s="3">
-        <v>-120.245</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
       <c r="E4" t="s">
         <v>41</v>
       </c>
@@ -17441,17 +17425,9 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>160.0</v>
-      </c>
-      <c r="B5" s="3">
-        <v>-106.9</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
       <c r="E5" t="s">
         <v>76</v>
       </c>
@@ -17460,134 +17436,54 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>180.0</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-104.6</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="B7" s="3">
-        <v>-97.1</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>220.0</v>
-      </c>
-      <c r="B8" s="3">
-        <v>-89.7</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>240.0</v>
-      </c>
-      <c r="B9" s="3">
-        <v>-79.9</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>260.0</v>
-      </c>
-      <c r="B10" s="3">
-        <v>-71.5</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>280.0</v>
-      </c>
-      <c r="B11" s="3">
-        <v>-59.0</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>300.0</v>
-      </c>
-      <c r="B12" s="3">
-        <v>-47.9</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>320.0</v>
-      </c>
-      <c r="B13" s="3">
-        <v>-33.1</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>340.0</v>
-      </c>
-      <c r="B14" s="3">
-        <v>-16.0</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Horiz</t>
-        </is>
-      </c>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>350.168</v>
-      </c>
-      <c r="B15" s="3">
-        <v>-7.761</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>

--- a/docs/files/rocscience/vp029.xlsx
+++ b/docs/files/rocscience/vp029.xlsx
@@ -13432,10 +13432,10 @@
         <v>0.0</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
